--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>128435492</v>
       </c>
       <c r="B5" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -899,53 +899,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128433199</v>
+        <v>128435492</v>
       </c>
       <c r="B4" t="n">
-        <v>5480</v>
+        <v>92650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101920</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Ög</t>
+          <t>Råbockamon, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517211</v>
+        <v>516951</v>
       </c>
       <c r="R4" t="n">
-        <v>6520958</v>
+        <v>6520951</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,63 +997,72 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128435492</v>
+        <v>128434028</v>
       </c>
       <c r="B5" t="n">
-        <v>92650</v>
+        <v>57833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råbockamon, Ög</t>
+          <t>Näverkärret, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516951</v>
+        <v>517187</v>
       </c>
       <c r="R5" t="n">
-        <v>6520951</v>
+        <v>6520946</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128434028</v>
+        <v>128434737</v>
       </c>
       <c r="B6" t="n">
-        <v>57833</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1154,24 +1161,25 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Näverkärret, Ög</t>
+          <t>Garpekärret, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517187</v>
+        <v>517155</v>
       </c>
       <c r="R6" t="n">
-        <v>6520946</v>
+        <v>6520895</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1203,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,27 +1248,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128434737</v>
+        <v>128435000</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>57670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1268,33 +1276,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Garpekärret, Ög</t>
+          <t>Råbockamon, Råbockamon, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517155</v>
+        <v>517116</v>
       </c>
       <c r="R7" t="n">
-        <v>6520895</v>
+        <v>6520907</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,62 +1348,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128435000</v>
+        <v>128433199</v>
       </c>
       <c r="B8" t="n">
-        <v>57670</v>
+        <v>5480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>101920</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Råbockamon, Råbockamon, Ög</t>
+          <t>Näverkärret, Näverkärret, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517116</v>
+        <v>517211</v>
       </c>
       <c r="R8" t="n">
-        <v>6520907</v>
+        <v>6520958</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Centimeterstora kantiga kläckhål på stående murken torraka av tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,6 +1463,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128433254</v>
       </c>
       <c r="B2" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128435492</v>
       </c>
       <c r="B4" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128434028</v>
       </c>
       <c r="B5" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,27 +1128,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128434737</v>
+        <v>128435000</v>
       </c>
       <c r="B6" t="n">
-        <v>5197</v>
+        <v>57682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1156,33 +1156,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Garpekärret, Ög</t>
+          <t>Råbockamon, Råbockamon, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517155</v>
+        <v>517116</v>
       </c>
       <c r="R6" t="n">
-        <v>6520895</v>
+        <v>6520907</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,39 +1228,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128435000</v>
+        <v>128434737</v>
       </c>
       <c r="B7" t="n">
-        <v>57670</v>
+        <v>5197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1276,25 +1268,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Råbockamon, Råbockamon, Ög</t>
+          <t>Garpekärret, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517116</v>
+        <v>517155</v>
       </c>
       <c r="R7" t="n">
-        <v>6520907</v>
+        <v>6520895</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,12 +1348,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -1128,27 +1128,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128435000</v>
+        <v>128434737</v>
       </c>
       <c r="B6" t="n">
-        <v>57682</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1156,25 +1156,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råbockamon, Råbockamon, Ög</t>
+          <t>Garpekärret, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517116</v>
+        <v>517155</v>
       </c>
       <c r="R6" t="n">
-        <v>6520907</v>
+        <v>6520895</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,39 +1236,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128434737</v>
+        <v>128435000</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>57682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1268,33 +1276,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Garpekärret, Ög</t>
+          <t>Råbockamon, Råbockamon, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517155</v>
+        <v>517116</v>
       </c>
       <c r="R7" t="n">
-        <v>6520895</v>
+        <v>6520907</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,12 +1348,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -1128,27 +1128,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128434737</v>
+        <v>128435000</v>
       </c>
       <c r="B6" t="n">
-        <v>5197</v>
+        <v>57682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1156,33 +1156,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Garpekärret, Ög</t>
+          <t>Råbockamon, Råbockamon, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517155</v>
+        <v>517116</v>
       </c>
       <c r="R6" t="n">
-        <v>6520895</v>
+        <v>6520907</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,39 +1228,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128435000</v>
+        <v>128434737</v>
       </c>
       <c r="B7" t="n">
-        <v>57682</v>
+        <v>5197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1276,25 +1268,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Råbockamon, Råbockamon, Ög</t>
+          <t>Garpekärret, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517116</v>
+        <v>517155</v>
       </c>
       <c r="R7" t="n">
-        <v>6520907</v>
+        <v>6520895</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,12 +1348,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128433254</v>
       </c>
       <c r="B2" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128435492</v>
       </c>
       <c r="B4" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128434028</v>
       </c>
       <c r="B5" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128435000</v>
       </c>
       <c r="B6" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128435492</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128435492</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -1128,27 +1128,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128435000</v>
+        <v>128434737</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1156,25 +1156,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råbockamon, Råbockamon, Ög</t>
+          <t>Garpekärret, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517116</v>
+        <v>517155</v>
       </c>
       <c r="R6" t="n">
-        <v>6520907</v>
+        <v>6520895</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,39 +1236,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128434737</v>
+        <v>128435000</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>57686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1268,33 +1276,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Garpekärret, Ög</t>
+          <t>Råbockamon, Råbockamon, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517155</v>
+        <v>517116</v>
       </c>
       <c r="R7" t="n">
-        <v>6520895</v>
+        <v>6520907</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,12 +1348,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128433254</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128435492</v>
       </c>
       <c r="B4" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128434028</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128435000</v>
       </c>
       <c r="B7" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128435492</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -1128,27 +1128,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128434737</v>
+        <v>128435000</v>
       </c>
       <c r="B6" t="n">
-        <v>5197</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1156,33 +1156,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Garpekärret, Ög</t>
+          <t>Råbockamon, Råbockamon, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517155</v>
+        <v>517116</v>
       </c>
       <c r="R6" t="n">
-        <v>6520895</v>
+        <v>6520907</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,39 +1228,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128435000</v>
+        <v>128434737</v>
       </c>
       <c r="B7" t="n">
-        <v>57713</v>
+        <v>5197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1276,25 +1268,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Råbockamon, Råbockamon, Ög</t>
+          <t>Garpekärret, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517116</v>
+        <v>517155</v>
       </c>
       <c r="R7" t="n">
-        <v>6520907</v>
+        <v>6520895</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,12 +1348,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -1128,27 +1128,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128435000</v>
+        <v>128434737</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1156,25 +1156,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råbockamon, Råbockamon, Ög</t>
+          <t>Garpekärret, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517116</v>
+        <v>517155</v>
       </c>
       <c r="R6" t="n">
-        <v>6520907</v>
+        <v>6520895</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,39 +1236,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128434737</v>
+        <v>128435000</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>57713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1268,33 +1276,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Garpekärret, Ög</t>
+          <t>Råbockamon, Råbockamon, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517155</v>
+        <v>517116</v>
       </c>
       <c r="R7" t="n">
-        <v>6520895</v>
+        <v>6520907</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,12 +1348,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128433254</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128435492</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128434028</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128435000</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128433254</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128435492</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128434028</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,27 +1128,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128435000</v>
+        <v>128434737</v>
       </c>
       <c r="B6" t="n">
-        <v>57717</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1156,25 +1156,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råbockamon, Råbockamon, Ög</t>
+          <t>Garpekärret, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517116</v>
+        <v>517155</v>
       </c>
       <c r="R6" t="n">
-        <v>6520907</v>
+        <v>6520895</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,39 +1236,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128434737</v>
+        <v>128435000</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1268,33 +1276,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Garpekärret, Ög</t>
+          <t>Råbockamon, Råbockamon, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517155</v>
+        <v>517116</v>
       </c>
       <c r="R7" t="n">
-        <v>6520895</v>
+        <v>6520907</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,12 +1348,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">

--- a/artfynd/A 40801-2025 artfynd.xlsx
+++ b/artfynd/A 40801-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128433254</v>
+        <v>128435492</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Ög</t>
+          <t>Råbockamon, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517214</v>
+        <v>516951</v>
       </c>
       <c r="R2" t="n">
-        <v>6520959</v>
+        <v>6520951</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +773,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128434912</v>
+        <v>128433254</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +796,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Garpekärret, Garpekärret, Ög</t>
+          <t>Näverkärret, Näverkärret, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517141</v>
+        <v>517214</v>
       </c>
       <c r="R3" t="n">
-        <v>6520909</v>
+        <v>6520959</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128435492</v>
+        <v>128435000</v>
       </c>
       <c r="B4" t="n">
-        <v>92805</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,40 +908,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Råbockamon, Ög</t>
+          <t>Råbockamon, Råbockamon, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516951</v>
+        <v>517116</v>
       </c>
       <c r="R4" t="n">
-        <v>6520951</v>
+        <v>6520907</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,44 +997,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128434028</v>
+        <v>128433995</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>4775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,11 +1042,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1056,13 +1057,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517187</v>
+        <v>517249</v>
       </c>
       <c r="R5" t="n">
-        <v>6520946</v>
+        <v>6520940</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,50 +1129,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128435000</v>
+        <v>128433199</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>5482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>101920</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råbockamon, Råbockamon, Ög</t>
+          <t>Näverkärret, Näverkärret, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517116</v>
+        <v>517211</v>
       </c>
       <c r="R6" t="n">
-        <v>6520907</v>
+        <v>6520958</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,15 +1218,21 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Centimeterstora kantiga kläckhål på stående murken torraka av tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1240,32 +1251,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128434737</v>
+        <v>128434028</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,25 +1284,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Garpekärret, Ög</t>
+          <t>Näverkärret, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517155</v>
+        <v>517187</v>
       </c>
       <c r="R7" t="n">
-        <v>6520895</v>
+        <v>6520946</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1323,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,54 +1370,58 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128433199</v>
+        <v>128433996</v>
       </c>
       <c r="B8" t="n">
-        <v>5480</v>
+        <v>5199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101920</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Ög</t>
+          <t>Näverkärret, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517211</v>
+        <v>517249</v>
       </c>
       <c r="R8" t="n">
-        <v>6520958</v>
+        <v>6520940</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,36 +1463,369 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Centimeterstora kantiga kläckhål på stående murken torraka av tall.</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128434737</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Garpekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>517155</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6520895</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128432828</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Näverkärret, Näverkärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>517220</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6520975</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Johan Holmgren</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Johan Holmgren</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128434912</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Garpekärret, Garpekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>517141</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6520909</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
